--- a/3th course/МИЭП/контрольная.xlsx
+++ b/3th course/МИЭП/контрольная.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bajsh\Desktop\university\3th course\МИЭП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC7929C-1D91-4EE2-9C58-D4ED5AD320D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82AC983-D83E-5642-83C7-413868BB0515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1" sheetId="1" r:id="rId1"/>
     <sheet name="Задание 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Задание 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>Магазины</t>
   </si>
@@ -72,14 +73,530 @@
     <t>t</t>
   </si>
   <si>
-    <t>Ŷ(t)</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>a₁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a₀ </t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Y(t) - Ŷ(t) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">|e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> |</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">  t|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) * 100%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">t - t̄ </t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[e </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - e </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">e </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> * e </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>t-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(t - t̄ ) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Скользящая средняя Ŷ(t) (m = 3)</t>
+  </si>
+  <si>
+    <r>
+      <t>Линейный тренд Y(t)=a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ​+a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​t</t>
+    </r>
+  </si>
+  <si>
+    <t>Поворотная точка</t>
+  </si>
+  <si>
+    <t>Случайность ост. комп.</t>
+  </si>
+  <si>
+    <t>d-критерий</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Так как d находится в интервале от нуля до </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1 (1,08)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> , то уровни ряда остатков сильно автокоррелированы.</t>
+    </r>
+  </si>
+  <si>
+    <t>R/S - критерий (2,7-3,7)</t>
+  </si>
+  <si>
+    <t>Так как значение R/S-критерия не попадает в границы, то гипотеза о нормально распределении отклоняется</t>
+  </si>
+  <si>
+    <t>СКО</t>
+  </si>
+  <si>
+    <t>СРЕДНЯЯ ПО МОДУЛЮ ОШИБКА</t>
+  </si>
+  <si>
+    <t>Модель имеет хорошую точность - средняя ошибка практически нулевая, а разброс предсказаний относительно невелик (около 12% от среднего значения ряда).</t>
+  </si>
+  <si>
+    <t>Точечный прогноз</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">t = </t>
+  </si>
+  <si>
+    <t>Интервальный прогноз</t>
+  </si>
+  <si>
+    <t>Погрешность</t>
+  </si>
+  <si>
+    <t>Верх. Граница</t>
+  </si>
+  <si>
+    <t>Нижняя Граница</t>
+  </si>
+  <si>
+    <t>Качество</t>
+  </si>
+  <si>
+    <t>Опыт работы в банковской сфере</t>
+  </si>
+  <si>
+    <t>Опыт работы в ИТ</t>
+  </si>
+  <si>
+    <t>Уровень образования</t>
+  </si>
+  <si>
+    <t>Опыт руководства людьми</t>
+  </si>
+  <si>
+    <t>Коммуникабельность</t>
+  </si>
+  <si>
+    <t>Стремление к саморазвитию</t>
+  </si>
+  <si>
+    <t>Ответственное отношение к делу</t>
+  </si>
+  <si>
+    <t>Личное обаяние</t>
+  </si>
+  <si>
+    <t>Эксперт 1</t>
+  </si>
+  <si>
+    <t>Сумма баллов</t>
+  </si>
+  <si>
+    <t>Эксперт 2</t>
+  </si>
+  <si>
+    <t>Эксперт 3</t>
+  </si>
+  <si>
+    <t>Относительный вес </t>
+  </si>
+  <si>
+    <t>Групповая оценка качеств каждого кандидата</t>
+  </si>
+  <si>
+    <t>Иванов И.И.</t>
+  </si>
+  <si>
+    <t>Петров П.П.</t>
+  </si>
+  <si>
+    <t>Сидоров С.С.</t>
+  </si>
+  <si>
+    <t>Интегральная оценка каждого претендента</t>
+  </si>
+  <si>
+    <t>ВЫВОД: НАИБОЛЕЕ ПОДХОДЯЩЕЙ КАНДИДАТУРОЙ ЯВЛЯЕТСЯ ПЕТРОВ П. П., ТАК КАК ЕГО ИНТЕГРАЛЬНАЯ ОЦЕНКА САМАЯ ВЫСОКАЯ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,13 +604,141 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -123,10 +768,71 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,6 +1251,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -552,7 +1259,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -990,6 +1696,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -997,7 +1704,440 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Сравнение фактических значений и прогнозируемых</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Фактические значение</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Задание 2'!$B$2:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0484-EA44-BF53-E2BB77F81E79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Прогнозируемое значение</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Задание 2'!$F$2:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>4.7833333333333314</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.004761904761903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.226190476190474</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.447619047619046</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.669047619047618</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20.890476190476189</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24.111904761904761</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27.333333333333332</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.554761904761904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33.776190476190479</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.99761904761904</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40.219047619047615</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>43.44047619047619</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46.661904761904765</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>49.883333333333326</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0484-EA44-BF53-E2BB77F81E79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="315771520"/>
+        <c:axId val="315770176"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="315771520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="315770176"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="315770176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="315771520"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1112,6 +2252,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1778,6 +2958,522 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2200,6 +3896,47 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>505046</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>119911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>705883</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>175436</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E7D6935-35F9-45E0-8D37-648535BE8685}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2472,18 +4209,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2512,7 +4249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2547,7 +4284,7 @@
         <v>10.245314467769175</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2570,7 +4307,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2593,7 +4330,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2616,7 +4353,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2639,7 +4376,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2662,7 +4399,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2685,7 +4422,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2708,7 +4445,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2731,7 +4468,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2754,7 +4491,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2777,7 +4514,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2808,141 +4545,1761 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD8D981A-6B70-492E-855F-F6A0B394F30D}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="10" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:21" ht="22" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10">
+        <f>SLOPE(B2:B16,A2:A16)</f>
+        <v>3.2214285714285715</v>
+      </c>
+      <c r="E2" s="10">
+        <f>INTERCEPT(B2:B16,A2:A16)</f>
+        <v>1.5619047619047599</v>
+      </c>
+      <c r="F2" s="10">
+        <f>$E$2 + $D$2 * A2</f>
+        <v>4.7833333333333314</v>
+      </c>
+      <c r="G2" s="11">
+        <f>B2-F2</f>
+        <v>1.2166666666666686</v>
+      </c>
+      <c r="H2" s="10">
+        <f xml:space="preserve"> G2^2</f>
+        <v>1.4802777777777825</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10">
+        <f>(ABS(G2)/ ABS(B2))*100</f>
+        <v>20.277777777777807</v>
+      </c>
+      <c r="M2" s="10">
+        <f>A2-AVERAGE($A$2:$A$16)</f>
+        <v>-7</v>
+      </c>
+      <c r="N2" s="10">
+        <f>M2^2</f>
+        <v>49</v>
+      </c>
+      <c r="O2" s="10">
+        <v>0</v>
+      </c>
+      <c r="P2" s="10" t="str">
+        <f>IF(SUM(O2:O16)&gt;(2*(15-2)/3-2*SQRT((16*15 - 29)/90)), "случайно", "не случайно")</f>
+        <v>случайно</v>
+      </c>
+      <c r="Q2" s="10">
+        <f>J17/H17</f>
+        <v>1.0703887412987194</v>
+      </c>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+    </row>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="10">
+        <f>(B2+B3+B4)/3</f>
+        <v>8</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10">
+        <f t="shared" ref="F3:F16" si="0">$E$2 + $D$2 * A3</f>
+        <v>8.004761904761903</v>
+      </c>
+      <c r="G3" s="11">
+        <f t="shared" ref="G3:G16" si="1">B3-F3</f>
+        <v>1.995238095238097</v>
+      </c>
+      <c r="H3" s="10">
+        <f>G3^2</f>
+        <v>3.9809750566893496</v>
+      </c>
+      <c r="I3" s="10">
+        <f>$G3-$G2</f>
+        <v>0.77857142857142847</v>
+      </c>
+      <c r="J3" s="10">
+        <f>I3^2</f>
+        <v>0.60617346938775496</v>
+      </c>
+      <c r="K3" s="10">
+        <f>G3*G2</f>
+        <v>2.4275396825396887</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3:L16" si="2">(ABS(G3)/ ABS(B3))*100</f>
+        <v>19.95238095238097</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" ref="M3:M16" si="3">A3-AVERAGE($A$2:$A$16)</f>
+        <v>-6</v>
+      </c>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N16" si="4">M3^2</f>
+        <v>36</v>
+      </c>
+      <c r="O3" s="10">
+        <f>IF(OR(AND(G3&gt;G2,G3&gt;G4),AND(G3&lt;G2,G3&lt;G4)),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+    </row>
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="10">
+        <f t="shared" ref="C4:C16" si="5">(B3+B4+B5)/3</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10">
+        <f t="shared" si="0"/>
+        <v>11.226190476190474</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.2261904761904745</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H16" si="6">G4^2</f>
+        <v>10.40830498866212</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" ref="I4:I16" si="7">$G4-$G3</f>
+        <v>-5.2214285714285715</v>
+      </c>
+      <c r="J4" s="10">
+        <f t="shared" ref="J4:J16" si="8">I4^2</f>
+        <v>27.263316326530614</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" ref="K4:K16" si="9">G4*G3</f>
+        <v>-6.4370181405895712</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="2"/>
+        <v>40.327380952380935</v>
+      </c>
+      <c r="M4" s="10">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+      <c r="N4" s="10">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="O4" s="10">
+        <f t="shared" ref="O4:O15" si="10">IF(OR(AND(G4&gt;G3,G4&gt;G5),AND(G4&lt;G3,G4&lt;G5)),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10">
+        <f t="shared" si="0"/>
+        <v>14.447619047619046</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.447619047619046</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="6"/>
+        <v>2.0956009070294739</v>
+      </c>
+      <c r="I5" s="10">
+        <f t="shared" si="7"/>
+        <v>1.7785714285714285</v>
+      </c>
+      <c r="J5" s="10">
+        <f t="shared" si="8"/>
+        <v>3.1633163265306119</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="9"/>
+        <v>4.6702947845804914</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="2"/>
+        <v>11.135531135531124</v>
+      </c>
+      <c r="M5" s="10">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="O5" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="10">
+        <f t="shared" si="5"/>
+        <v>15.666666666666666</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
+        <f t="shared" si="0"/>
+        <v>17.669047619047618</v>
+      </c>
+      <c r="G6" s="11">
+        <f t="shared" si="1"/>
+        <v>-2.6690476190476176</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="6"/>
+        <v>7.1238151927437565</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="7"/>
+        <v>-1.2214285714285715</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="8"/>
+        <v>1.4918877551020411</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="9"/>
+        <v>3.8637641723355944</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="2"/>
+        <v>17.793650793650784</v>
+      </c>
+      <c r="M6" s="10">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="O6" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="10">
+        <f t="shared" si="5"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10">
+        <f t="shared" si="0"/>
+        <v>20.890476190476189</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" si="1"/>
+        <v>-1.8904761904761891</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" si="6"/>
+        <v>3.5739002267573645</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" si="7"/>
+        <v>0.77857142857142847</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" si="8"/>
+        <v>0.60617346938775496</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="9"/>
+        <v>5.0457709750566826</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="2"/>
+        <v>9.9498746867167842</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" si="3"/>
+        <v>-2</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="O7" s="10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="10">
+        <f t="shared" si="5"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>24.111904761904761</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="1"/>
+        <v>0.88809523809523938</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="6"/>
+        <v>0.78871315192743996</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="7"/>
+        <v>2.7785714285714285</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="8"/>
+        <v>7.7204591836734684</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="9"/>
+        <v>-1.6789229024943322</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5523809523809575</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="10">
+        <f t="shared" si="5"/>
+        <v>28.333333333333332</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10">
+        <f t="shared" si="0"/>
+        <v>27.333333333333332</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.33333333333333215</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="6"/>
+        <v>0.11111111111111033</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="7"/>
+        <v>-1.2214285714285715</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="8"/>
+        <v>1.4918877551020411</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="9"/>
+        <v>-0.29603174603174542</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="2"/>
+        <v>1.2345679012345634</v>
+      </c>
+      <c r="M9" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="10">
+        <f t="shared" si="5"/>
+        <v>31.666666666666668</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10">
+        <f t="shared" si="0"/>
+        <v>30.554761904761904</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" si="1"/>
+        <v>2.4452380952380963</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="6"/>
+        <v>5.9791893424036333</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="7"/>
+        <v>2.7785714285714285</v>
+      </c>
+      <c r="J10" s="10">
+        <f t="shared" si="8"/>
+        <v>7.7204591836734684</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="9"/>
+        <v>-0.81507936507936252</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="2"/>
+        <v>7.4098124098124138</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="10">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="10">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10">
+        <f t="shared" si="0"/>
+        <v>33.776190476190479</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="1"/>
+        <v>1.2238095238095212</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="6"/>
+        <v>1.497709750566887</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="7"/>
+        <v>-1.2214285714285751</v>
+      </c>
+      <c r="J11" s="10">
+        <f t="shared" si="8"/>
+        <v>1.4918877551020497</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="9"/>
+        <v>2.9925056689342355</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4965986394557751</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="N11" s="10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="O11" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="10">
+        <f t="shared" si="5"/>
+        <v>40.666666666666664</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10">
+        <f t="shared" si="0"/>
+        <v>36.99761904761904</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="1"/>
+        <v>3.0023809523809604</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="6"/>
+        <v>9.0142913832200033</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="7"/>
+        <v>1.7785714285714391</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" si="8"/>
+        <v>3.1633163265306496</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="9"/>
+        <v>3.67434240362812</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" si="2"/>
+        <v>7.5059523809524009</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="O12" s="10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="10">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10">
+        <f t="shared" si="0"/>
+        <v>40.219047619047615</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="1"/>
+        <v>6.7809523809523853</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="6"/>
+        <v>45.981315192743821</v>
+      </c>
+      <c r="I13" s="10">
+        <f t="shared" si="7"/>
+        <v>3.7785714285714249</v>
+      </c>
+      <c r="J13" s="10">
+        <f t="shared" si="8"/>
+        <v>14.2776020408163</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="9"/>
+        <v>20.359002267573764</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="2"/>
+        <v>14.427558257345503</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="O13" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="10">
+        <f t="shared" si="5"/>
+        <v>44.333333333333336</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
+        <f t="shared" si="0"/>
+        <v>43.44047619047619</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="1"/>
+        <v>1.5595238095238102</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="6"/>
+        <v>2.4321145124716574</v>
+      </c>
+      <c r="I14" s="10">
+        <f t="shared" si="7"/>
+        <v>-5.2214285714285751</v>
+      </c>
+      <c r="J14" s="10">
+        <f t="shared" si="8"/>
+        <v>27.263316326530649</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="9"/>
+        <v>10.575056689342414</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4656084656084669</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="O14" s="10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="10">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10">
+        <f t="shared" si="0"/>
+        <v>46.661904761904765</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="1"/>
+        <v>-5.6619047619047649</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="6"/>
+        <v>32.05716553287985</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="7"/>
+        <v>-7.2214285714285751</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="8"/>
+        <v>52.14903061224495</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="9"/>
+        <v>-8.8298752834467198</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="2"/>
+        <v>13.809523809523816</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="O15" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>46</v>
       </c>
+      <c r="C16" s="10">
+        <f t="shared" si="5"/>
+        <v>29</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10">
+        <f t="shared" si="0"/>
+        <v>49.883333333333326</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.8833333333333258</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="6"/>
+        <v>15.080277777777718</v>
+      </c>
+      <c r="I16" s="10">
+        <f t="shared" si="7"/>
+        <v>1.7785714285714391</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="8"/>
+        <v>3.1633163265306496</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="9"/>
+        <v>21.987063492063459</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="2"/>
+        <v>8.4420289855072301</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <f>SUM(A2:A16)</f>
+        <v>120</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="12">
+        <f>SUM(H2:H16)</f>
+        <v>141.60476190476197</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="12">
+        <f>SUM(J3:J16)</f>
+        <v>151.57214285714304</v>
+      </c>
+      <c r="K17" s="12">
+        <f>SUM(K3:K16)</f>
+        <v>57.538412698412728</v>
+      </c>
+      <c r="L17" s="12">
+        <f>SUM(L2:L16)</f>
+        <v>182.78062810025955</v>
+      </c>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+    </row>
+    <row r="20" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="16">
+        <f>(MAX(G2:G16) - MIN(G2:G16))/ STDEV(G2:G16)</f>
+        <v>3.9124175987739038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="G22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="G23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23">
+        <f>1.05*B27</f>
+        <v>3.3393674550728925</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="10">
+        <f>F2-H24</f>
+        <v>1.5619047619047599</v>
+      </c>
+      <c r="H24" s="10">
+        <f>F3-F2</f>
+        <v>3.2214285714285715</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="F25">
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <f>$G$24+$H$24*$F25</f>
+        <v>53.104761904761901</v>
+      </c>
+      <c r="J25">
+        <v>16</v>
+      </c>
+      <c r="K25">
+        <f>G25+L23</f>
+        <v>56.44412935983479</v>
+      </c>
+      <c r="L25">
+        <f>G25-L23</f>
+        <v>49.765394449689012</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>17</v>
+      </c>
+      <c r="G26">
+        <f>$G$24+$H$24*$F26</f>
+        <v>56.326190476190476</v>
+      </c>
+      <c r="J26">
+        <v>17</v>
+      </c>
+      <c r="K26">
+        <f>G26+L23</f>
+        <v>59.665557931263365</v>
+      </c>
+      <c r="L26">
+        <f>G26-L23</f>
+        <v>52.986823021117587</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <f>STDEV(G2:G16)</f>
+        <v>3.1803499572122784</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <f>ABS(SUM(G2:G16)/COUNT(G2:G16))</f>
+        <v>1.8947806286936005E-15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" s="14"/>
+    </row>
+    <row r="30" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="14"/>
+      <c r="C30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C22:D25"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="C30:E33"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="Q3:U5"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:C21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BCA3E0-E705-2F48-9C0B-E6DCC10A06A4}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <f>E2/$E$10</f>
+        <v>0.15527950310559005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E9" si="0">SUM(B3:D3)</f>
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F9" si="1">E3/$E$10</f>
+        <v>0.11801242236024845</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>0.13043478260869565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>0.12422360248447205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>9.3167701863354033E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>0.11801242236024845</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0.16770186335403728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>9.3167701863354033E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E10" s="7">
+        <f>SUM(E2:E9)</f>
+        <v>161</v>
+      </c>
+      <c r="F10" s="7">
+        <f>SUM(F2:F9)</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <f>AVERAGE(5,5,5)</f>
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <f>AVERAGE(3,2,2)</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="D15">
+        <f>AVERAGE(3,4,4)</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <f>AVERAGE(3,4,3)</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(5,5,4)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D16">
+        <f>AVERAGE(2,2,1)</f>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <f>AVERAGE(4,4,4)</f>
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <f>AVERAGE(4,5,5)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D17">
+        <f>AVERAGE(5,4,4)</f>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <f>AVERAGE(3,4,2)</f>
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <f>AVERAGE(5,5,5)</f>
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <f>AVERAGE(3,4,4)</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <f>AVERAGE(5,3,3)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="C19">
+        <f>AVERAGE(4,5,5)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D19">
+        <f>AVERAGE(5,4,4)</f>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <f>AVERAGE(5,3,4)</f>
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <f>AVERAGE(3,2,4)</f>
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <f>AVERAGE(5,4,5)</f>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <f>AVERAGE(5,3,3)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="C21">
+        <f>AVERAGE(4,5,5)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D21">
+        <f>AVERAGE(5,5,4)</f>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <f>AVERAGE(4,4,4)</f>
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <f>AVERAGE(3,4,3)</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="D22">
+        <f>AVERAGE(5,3,5)</f>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <f>F2*B15</f>
+        <v>0.77639751552795022</v>
+      </c>
+      <c r="C27">
+        <f>F2*C15</f>
+        <v>0.36231884057971014</v>
+      </c>
+      <c r="D27">
+        <f>F2*D15</f>
+        <v>0.56935817805383016</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <f>F3*B16</f>
+        <v>0.39337474120082816</v>
+      </c>
+      <c r="C28">
+        <f t="shared" ref="C28:C34" si="2">F3*C16</f>
+        <v>0.55072463768115942</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ref="D28:D34" si="3">F3*D16</f>
+        <v>0.19668737060041408</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ref="B29:B34" si="4">F4*B17</f>
+        <v>0.52173913043478259</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="3"/>
+        <v>0.56521739130434778</v>
+      </c>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="4"/>
+        <v>0.37267080745341613</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="3"/>
+        <v>0.45548654244306414</v>
+      </c>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="4"/>
+        <v>0.34161490683229812</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="3"/>
+        <v>0.40372670807453409</v>
+      </c>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="4"/>
+        <v>0.47204968944099379</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>0.35403726708074534</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="3"/>
+        <v>0.55072463768115942</v>
+      </c>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="4"/>
+        <v>0.6149068322981367</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>0.78260869565217406</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="3"/>
+        <v>0.78260869565217406</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>8</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="4"/>
+        <v>0.37267080745341613</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>0.3105590062111801</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="3"/>
+        <v>0.40372670807453409</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="7">
+        <f>SUM(B27:B34)</f>
+        <v>3.8654244306418213</v>
+      </c>
+      <c r="C35" s="7">
+        <f t="shared" ref="C35:D35" si="5">SUM(C27:C34)</f>
+        <v>4.0248447204968949</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="5"/>
+        <v>3.9275362318840576</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="F28:H32"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>